--- a/artfynd/A 37476-2026 artfynd.xlsx
+++ b/artfynd/A 37476-2026 artfynd.xlsx
@@ -1622,7 +1622,7 @@
         <v>136583113</v>
       </c>
       <c r="B10" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37476-2026 artfynd.xlsx
+++ b/artfynd/A 37476-2026 artfynd.xlsx
@@ -1622,7 +1622,7 @@
         <v>136583113</v>
       </c>
       <c r="B10" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37476-2026 artfynd.xlsx
+++ b/artfynd/A 37476-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136583114</v>
       </c>
       <c r="B3" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136480982</v>
       </c>
       <c r="B4" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136480983</v>
       </c>
       <c r="B5" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>136480984</v>
       </c>
       <c r="B6" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136480953</v>
       </c>
       <c r="B7" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>136480954</v>
       </c>
       <c r="B8" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136583113</v>
       </c>
       <c r="B10" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37476-2026 artfynd.xlsx
+++ b/artfynd/A 37476-2026 artfynd.xlsx
@@ -1622,7 +1622,7 @@
         <v>136583113</v>
       </c>
       <c r="B10" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37476-2026 artfynd.xlsx
+++ b/artfynd/A 37476-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136583114</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136480982</v>
       </c>
       <c r="B4" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136480983</v>
       </c>
       <c r="B5" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>136480984</v>
       </c>
       <c r="B6" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136480953</v>
       </c>
       <c r="B7" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>136480954</v>
       </c>
       <c r="B8" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136583113</v>
       </c>
       <c r="B10" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37476-2026 artfynd.xlsx
+++ b/artfynd/A 37476-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136583114</v>
       </c>
       <c r="B3" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136480982</v>
       </c>
       <c r="B4" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136480983</v>
       </c>
       <c r="B5" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>136480984</v>
       </c>
       <c r="B6" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136480953</v>
       </c>
       <c r="B7" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>136480954</v>
       </c>
       <c r="B8" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136583113</v>
       </c>
       <c r="B10" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37476-2026 artfynd.xlsx
+++ b/artfynd/A 37476-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136583114</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136480982</v>
       </c>
       <c r="B4" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136480983</v>
       </c>
       <c r="B5" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>136480984</v>
       </c>
       <c r="B6" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136480953</v>
       </c>
       <c r="B7" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>136480954</v>
       </c>
       <c r="B8" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136583113</v>
       </c>
       <c r="B10" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37476-2026 artfynd.xlsx
+++ b/artfynd/A 37476-2026 artfynd.xlsx
@@ -1622,7 +1622,7 @@
         <v>136583113</v>
       </c>
       <c r="B10" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37476-2026 artfynd.xlsx
+++ b/artfynd/A 37476-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136583114</v>
       </c>
       <c r="B3" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136480982</v>
       </c>
       <c r="B4" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136480983</v>
       </c>
       <c r="B5" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>136480984</v>
       </c>
       <c r="B6" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136480953</v>
       </c>
       <c r="B7" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>136480954</v>
       </c>
       <c r="B8" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136583113</v>
       </c>
       <c r="B10" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37476-2026 artfynd.xlsx
+++ b/artfynd/A 37476-2026 artfynd.xlsx
@@ -1622,7 +1622,7 @@
         <v>136583113</v>
       </c>
       <c r="B10" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37476-2026 artfynd.xlsx
+++ b/artfynd/A 37476-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136583114</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136583113</v>
       </c>
       <c r="B10" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
